--- a/outputs/49196.xlsx
+++ b/outputs/49196.xlsx
@@ -345,16 +345,20 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -611,946 +615,946 @@
   <dimension ref="C1:L47"/>
   <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="8.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="13.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="13.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="8.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="13.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="13.33"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C2" s="2" t="str">
-        <f aca="false">LEFT(K2,2)&amp;"/"&amp;MID(K2,4,2)&amp;"/"&amp;"20"&amp;MID(K2,7,2)&amp;MID(K2,FIND(" ",K2,1),6)</f>
-        <v>21/11/2021 14:28</v>
-      </c>
-      <c r="D2" s="2" t="str">
+      <c r="C2" s="3" t="str">
+        <f aca="false">LEFT(K2,2)&amp;"/"&amp;MID(K2,4,2)&amp;"/"&amp;MID(K2,7,2)&amp;MID(K2,FIND(" ",K2,1),6)</f>
+        <v>21/11/21 14:28</v>
+      </c>
+      <c r="D2" s="3" t="str">
         <f aca="false">TEXT(C2,"mmm")</f>
-        <v>21/11/2021 14:28</v>
-      </c>
-      <c r="E2" s="2" t="e">
+        <v>21/11/21 14:28</v>
+      </c>
+      <c r="E2" s="3" t="e">
         <f aca="false">WEEKNUM(C2,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="K2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="0" t="s">
+      <c r="L2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C3" s="2" t="str">
-        <f aca="false">LEFT(K3,2)&amp;"/"&amp;MID(K3,4,2)&amp;"/"&amp;"20"&amp;MID(K3,7,2)&amp;MID(K3,FIND(" ",K3,1),6)</f>
-        <v>22/11/2021 06:00</v>
-      </c>
-      <c r="D3" s="2" t="str">
+      <c r="C3" s="3" t="str">
+        <f aca="false">LEFT(K3,2)&amp;"/"&amp;MID(K3,4,2)&amp;"/"&amp;MID(K3,7,2)&amp;MID(K3,FIND(" ",K3,1),6)</f>
+        <v>22/11/21 06:00</v>
+      </c>
+      <c r="D3" s="3" t="str">
         <f aca="false">TEXT(C3,"mmm")</f>
-        <v>22/11/2021 06:00</v>
-      </c>
-      <c r="E3" s="2" t="e">
+        <v>22/11/21 06:00</v>
+      </c>
+      <c r="E3" s="3" t="e">
         <f aca="false">WEEKNUM(C3,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K3" s="0" t="s">
+      <c r="K3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="0" t="s">
+      <c r="L3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="2" t="str">
-        <f aca="false">LEFT(K4,2)&amp;"/"&amp;MID(K4,4,2)&amp;"/"&amp;"20"&amp;MID(K4,7,2)&amp;MID(K4,FIND(" ",K4,1),6)</f>
-        <v>23/11/2021 06:00</v>
-      </c>
-      <c r="D4" s="2" t="str">
+      <c r="C4" s="3" t="str">
+        <f aca="false">LEFT(K4,2)&amp;"/"&amp;MID(K4,4,2)&amp;"/"&amp;MID(K4,7,2)&amp;MID(K4,FIND(" ",K4,1),6)</f>
+        <v>23/11/21 06:00</v>
+      </c>
+      <c r="D4" s="3" t="str">
         <f aca="false">TEXT(C4,"mmm")</f>
-        <v>23/11/2021 06:00</v>
-      </c>
-      <c r="E4" s="2" t="e">
+        <v>23/11/21 06:00</v>
+      </c>
+      <c r="E4" s="3" t="e">
         <f aca="false">WEEKNUM(C4,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K4" s="0" t="s">
+      <c r="K4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="0" t="s">
+      <c r="L4" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="2" t="str">
-        <f aca="false">LEFT(K5,2)&amp;"/"&amp;MID(K5,4,2)&amp;"/"&amp;"20"&amp;MID(K5,7,2)&amp;MID(K5,FIND(" ",K5,1),6)</f>
-        <v>23/11/2021 22:04</v>
-      </c>
-      <c r="D5" s="2" t="str">
+      <c r="C5" s="3" t="str">
+        <f aca="false">LEFT(K5,2)&amp;"/"&amp;MID(K5,4,2)&amp;"/"&amp;MID(K5,7,2)&amp;MID(K5,FIND(" ",K5,1),6)</f>
+        <v>23/11/21 22:04</v>
+      </c>
+      <c r="D5" s="3" t="str">
         <f aca="false">TEXT(C5,"mmm")</f>
-        <v>23/11/2021 22:04</v>
-      </c>
-      <c r="E5" s="2" t="e">
+        <v>23/11/21 22:04</v>
+      </c>
+      <c r="E5" s="3" t="e">
         <f aca="false">WEEKNUM(C5,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K5" s="0" t="s">
+      <c r="K5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="0" t="s">
+      <c r="L5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="2" t="str">
-        <f aca="false">LEFT(K6,2)&amp;"/"&amp;MID(K6,4,2)&amp;"/"&amp;"20"&amp;MID(K6,7,2)&amp;MID(K6,FIND(" ",K6,1),6)</f>
-        <v>24/11/2021 18:00</v>
-      </c>
-      <c r="D6" s="2" t="str">
+      <c r="C6" s="3" t="str">
+        <f aca="false">LEFT(K6,2)&amp;"/"&amp;MID(K6,4,2)&amp;"/"&amp;MID(K6,7,2)&amp;MID(K6,FIND(" ",K6,1),6)</f>
+        <v>24/11/21 18:00</v>
+      </c>
+      <c r="D6" s="3" t="str">
         <f aca="false">TEXT(C6,"mmm")</f>
-        <v>24/11/2021 18:00</v>
-      </c>
-      <c r="E6" s="2" t="e">
+        <v>24/11/21 18:00</v>
+      </c>
+      <c r="E6" s="3" t="e">
         <f aca="false">WEEKNUM(C6,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K6" s="0" t="s">
+      <c r="K6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L6" s="0" t="s">
+      <c r="L6" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="2" t="str">
-        <f aca="false">LEFT(K7,2)&amp;"/"&amp;MID(K7,4,2)&amp;"/"&amp;"20"&amp;MID(K7,7,2)&amp;MID(K7,FIND(" ",K7,1),6)</f>
-        <v>25/11/2021 18:00</v>
-      </c>
-      <c r="D7" s="2" t="str">
+      <c r="C7" s="3" t="str">
+        <f aca="false">LEFT(K7,2)&amp;"/"&amp;MID(K7,4,2)&amp;"/"&amp;MID(K7,7,2)&amp;MID(K7,FIND(" ",K7,1),6)</f>
+        <v>25/11/21 18:00</v>
+      </c>
+      <c r="D7" s="3" t="str">
         <f aca="false">TEXT(C7,"mmm")</f>
-        <v>25/11/2021 18:00</v>
-      </c>
-      <c r="E7" s="2" t="e">
+        <v>25/11/21 18:00</v>
+      </c>
+      <c r="E7" s="3" t="e">
         <f aca="false">WEEKNUM(C7,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K7" s="0" t="s">
+      <c r="K7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L7" s="0" t="s">
+      <c r="L7" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="2" t="str">
-        <f aca="false">LEFT(K8,2)&amp;"/"&amp;MID(K8,4,2)&amp;"/"&amp;"20"&amp;MID(K8,7,2)&amp;MID(K8,FIND(" ",K8,1),6)</f>
-        <v>26/11/2021 10:13</v>
-      </c>
-      <c r="D8" s="2" t="str">
+      <c r="C8" s="3" t="str">
+        <f aca="false">LEFT(K8,2)&amp;"/"&amp;MID(K8,4,2)&amp;"/"&amp;MID(K8,7,2)&amp;MID(K8,FIND(" ",K8,1),6)</f>
+        <v>26/11/21 10:13</v>
+      </c>
+      <c r="D8" s="3" t="str">
         <f aca="false">TEXT(C8,"mmm")</f>
-        <v>26/11/2021 10:13</v>
-      </c>
-      <c r="E8" s="2" t="e">
+        <v>26/11/21 10:13</v>
+      </c>
+      <c r="E8" s="3" t="e">
         <f aca="false">WEEKNUM(C8,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K8" s="0" t="s">
+      <c r="K8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L8" s="0" t="s">
+      <c r="L8" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="2" t="str">
-        <f aca="false">LEFT(K9,2)&amp;"/"&amp;MID(K9,4,2)&amp;"/"&amp;"20"&amp;MID(K9,7,2)&amp;MID(K9,FIND(" ",K9,1),6)</f>
-        <v>29/11/2021 19:18</v>
-      </c>
-      <c r="D9" s="2" t="str">
+      <c r="C9" s="3" t="str">
+        <f aca="false">LEFT(K9,2)&amp;"/"&amp;MID(K9,4,2)&amp;"/"&amp;MID(K9,7,2)&amp;MID(K9,FIND(" ",K9,1),6)</f>
+        <v>29/11/21 19:18</v>
+      </c>
+      <c r="D9" s="3" t="str">
         <f aca="false">TEXT(C9,"mmm")</f>
-        <v>29/11/2021 19:18</v>
-      </c>
-      <c r="E9" s="2" t="e">
+        <v>29/11/21 19:18</v>
+      </c>
+      <c r="E9" s="3" t="e">
         <f aca="false">WEEKNUM(C9,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K9" s="0" t="s">
+      <c r="K9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L9" s="0" t="s">
+      <c r="L9" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="2" t="str">
-        <f aca="false">LEFT(K10,2)&amp;"/"&amp;MID(K10,4,2)&amp;"/"&amp;"20"&amp;MID(K10,7,2)&amp;MID(K10,FIND(" ",K10,1),6)</f>
-        <v>30/11/2021 05:04</v>
-      </c>
-      <c r="D10" s="2" t="str">
+      <c r="C10" s="3" t="str">
+        <f aca="false">LEFT(K10,2)&amp;"/"&amp;MID(K10,4,2)&amp;"/"&amp;MID(K10,7,2)&amp;MID(K10,FIND(" ",K10,1),6)</f>
+        <v>30/11/21 05:04</v>
+      </c>
+      <c r="D10" s="3" t="str">
         <f aca="false">TEXT(C10,"mmm")</f>
-        <v>30/11/2021 05:04</v>
-      </c>
-      <c r="E10" s="2" t="e">
+        <v>30/11/21 05:04</v>
+      </c>
+      <c r="E10" s="3" t="e">
         <f aca="false">WEEKNUM(C10,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K10" s="0" t="s">
+      <c r="K10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="L10" s="0" t="s">
+      <c r="L10" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="2" t="str">
-        <f aca="false">LEFT(K11,2)&amp;"/"&amp;MID(K11,4,2)&amp;"/"&amp;"20"&amp;MID(K11,7,2)&amp;MID(K11,FIND(" ",K11,1),6)</f>
-        <v>30/11/2021 06:00</v>
-      </c>
-      <c r="D11" s="2" t="str">
+      <c r="C11" s="3" t="str">
+        <f aca="false">LEFT(K11,2)&amp;"/"&amp;MID(K11,4,2)&amp;"/"&amp;MID(K11,7,2)&amp;MID(K11,FIND(" ",K11,1),6)</f>
+        <v>30/11/21 06:00</v>
+      </c>
+      <c r="D11" s="3" t="str">
         <f aca="false">TEXT(C11,"mmm")</f>
-        <v>30/11/2021 06:00</v>
-      </c>
-      <c r="E11" s="2" t="e">
+        <v>30/11/21 06:00</v>
+      </c>
+      <c r="E11" s="3" t="e">
         <f aca="false">WEEKNUM(C11,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K11" s="0" t="s">
+      <c r="K11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L11" s="0" t="s">
+      <c r="L11" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C12" s="2" t="str">
-        <f aca="false">LEFT(K12,2)&amp;"/"&amp;MID(K12,4,2)&amp;"/"&amp;"20"&amp;MID(K12,7,2)&amp;MID(K12,FIND(" ",K12,1),6)</f>
-        <v>01/12/2021 00:02</v>
-      </c>
-      <c r="D12" s="2" t="str">
+      <c r="C12" s="3" t="str">
+        <f aca="false">LEFT(K12,2)&amp;"/"&amp;MID(K12,4,2)&amp;"/"&amp;MID(K12,7,2)&amp;MID(K12,FIND(" ",K12,1),6)</f>
+        <v>01/12/21 00:02</v>
+      </c>
+      <c r="D12" s="3" t="str">
         <f aca="false">TEXT(C12,"mmm")</f>
         <v>Jan</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="3" t="n">
         <f aca="false">WEEKNUM(C12,21)</f>
         <v>2</v>
       </c>
-      <c r="K12" s="0" t="s">
+      <c r="K12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L12" s="0" t="s">
+      <c r="L12" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="2" t="str">
-        <f aca="false">LEFT(K13,2)&amp;"/"&amp;MID(K13,4,2)&amp;"/"&amp;"20"&amp;MID(K13,7,2)&amp;MID(K13,FIND(" ",K13,1),6)</f>
-        <v>01/12/2021 06:00</v>
-      </c>
-      <c r="D13" s="2" t="str">
+      <c r="C13" s="3" t="str">
+        <f aca="false">LEFT(K13,2)&amp;"/"&amp;MID(K13,4,2)&amp;"/"&amp;MID(K13,7,2)&amp;MID(K13,FIND(" ",K13,1),6)</f>
+        <v>01/12/21 06:00</v>
+      </c>
+      <c r="D13" s="3" t="str">
         <f aca="false">TEXT(C13,"mmm")</f>
         <v>Jan</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="3" t="n">
         <f aca="false">WEEKNUM(C13,21)</f>
         <v>2</v>
       </c>
-      <c r="K13" s="0" t="s">
+      <c r="K13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L13" s="0" t="s">
+      <c r="L13" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="2" t="str">
-        <f aca="false">LEFT(K14,2)&amp;"/"&amp;MID(K14,4,2)&amp;"/"&amp;"20"&amp;MID(K14,7,2)&amp;MID(K14,FIND(" ",K14,1),6)</f>
-        <v>02/12/2021 01:43</v>
-      </c>
-      <c r="D14" s="2" t="str">
+      <c r="C14" s="3" t="str">
+        <f aca="false">LEFT(K14,2)&amp;"/"&amp;MID(K14,4,2)&amp;"/"&amp;MID(K14,7,2)&amp;MID(K14,FIND(" ",K14,1),6)</f>
+        <v>02/12/21 01:43</v>
+      </c>
+      <c r="D14" s="3" t="str">
         <f aca="false">TEXT(C14,"mmm")</f>
         <v>Feb</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="3" t="n">
         <f aca="false">WEEKNUM(C14,21)</f>
         <v>6</v>
       </c>
-      <c r="K14" s="0" t="s">
+      <c r="K14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L14" s="0" t="s">
+      <c r="L14" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C15" s="2" t="str">
-        <f aca="false">LEFT(K15,2)&amp;"/"&amp;MID(K15,4,2)&amp;"/"&amp;"20"&amp;MID(K15,7,2)&amp;MID(K15,FIND(" ",K15,1),6)</f>
-        <v>02/12/2021 18:00</v>
-      </c>
-      <c r="D15" s="2" t="str">
+      <c r="C15" s="3" t="str">
+        <f aca="false">LEFT(K15,2)&amp;"/"&amp;MID(K15,4,2)&amp;"/"&amp;MID(K15,7,2)&amp;MID(K15,FIND(" ",K15,1),6)</f>
+        <v>02/12/21 18:00</v>
+      </c>
+      <c r="D15" s="3" t="str">
         <f aca="false">TEXT(C15,"mmm")</f>
         <v>Feb</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" s="3" t="n">
         <f aca="false">WEEKNUM(C15,21)</f>
         <v>6</v>
       </c>
-      <c r="K15" s="0" t="s">
+      <c r="K15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L15" s="0" t="s">
+      <c r="L15" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C16" s="2" t="str">
-        <f aca="false">LEFT(K16,2)&amp;"/"&amp;MID(K16,4,2)&amp;"/"&amp;"20"&amp;MID(K16,7,2)&amp;MID(K16,FIND(" ",K16,1),6)</f>
-        <v>03/12/2021 18:00</v>
-      </c>
-      <c r="D16" s="2" t="str">
+      <c r="C16" s="3" t="str">
+        <f aca="false">LEFT(K16,2)&amp;"/"&amp;MID(K16,4,2)&amp;"/"&amp;MID(K16,7,2)&amp;MID(K16,FIND(" ",K16,1),6)</f>
+        <v>03/12/21 18:00</v>
+      </c>
+      <c r="D16" s="3" t="str">
         <f aca="false">TEXT(C16,"mmm")</f>
         <v>Mar</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" s="3" t="n">
         <f aca="false">WEEKNUM(C16,21)</f>
         <v>10</v>
       </c>
-      <c r="K16" s="0" t="s">
+      <c r="K16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L16" s="0" t="s">
+      <c r="L16" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C17" s="2" t="str">
-        <f aca="false">LEFT(K17,2)&amp;"/"&amp;MID(K17,4,2)&amp;"/"&amp;"20"&amp;MID(K17,7,2)&amp;MID(K17,FIND(" ",K17,1),6)</f>
-        <v>04/12/2021 11:43</v>
-      </c>
-      <c r="D17" s="2" t="str">
+      <c r="C17" s="3" t="str">
+        <f aca="false">LEFT(K17,2)&amp;"/"&amp;MID(K17,4,2)&amp;"/"&amp;MID(K17,7,2)&amp;MID(K17,FIND(" ",K17,1),6)</f>
+        <v>04/12/21 11:43</v>
+      </c>
+      <c r="D17" s="3" t="str">
         <f aca="false">TEXT(C17,"mmm")</f>
         <v>Apr</v>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" s="3" t="n">
         <f aca="false">WEEKNUM(C17,21)</f>
         <v>15</v>
       </c>
-      <c r="K17" s="0" t="s">
+      <c r="K17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L17" s="0" t="s">
+      <c r="L17" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="2" t="str">
-        <f aca="false">LEFT(K18,2)&amp;"/"&amp;MID(K18,4,2)&amp;"/"&amp;"20"&amp;MID(K18,7,2)&amp;MID(K18,FIND(" ",K18,1),6)</f>
-        <v>08/12/2021 00:54</v>
-      </c>
-      <c r="D18" s="2" t="str">
+      <c r="C18" s="3" t="str">
+        <f aca="false">LEFT(K18,2)&amp;"/"&amp;MID(K18,4,2)&amp;"/"&amp;MID(K18,7,2)&amp;MID(K18,FIND(" ",K18,1),6)</f>
+        <v>08/12/21 00:54</v>
+      </c>
+      <c r="D18" s="3" t="str">
         <f aca="false">TEXT(C18,"mmm")</f>
         <v>Aug</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" s="3" t="n">
         <f aca="false">WEEKNUM(C18,21)</f>
         <v>32</v>
       </c>
-      <c r="K18" s="0" t="s">
+      <c r="K18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L18" s="0" t="s">
+      <c r="L18" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C19" s="2" t="str">
-        <f aca="false">LEFT(K19,2)&amp;"/"&amp;MID(K19,4,2)&amp;"/"&amp;"20"&amp;MID(K19,7,2)&amp;MID(K19,FIND(" ",K19,1),6)</f>
-        <v>08/12/2021 06:00</v>
-      </c>
-      <c r="D19" s="2" t="str">
+      <c r="C19" s="3" t="str">
+        <f aca="false">LEFT(K19,2)&amp;"/"&amp;MID(K19,4,2)&amp;"/"&amp;MID(K19,7,2)&amp;MID(K19,FIND(" ",K19,1),6)</f>
+        <v>08/12/21 06:00</v>
+      </c>
+      <c r="D19" s="3" t="str">
         <f aca="false">TEXT(C19,"mmm")</f>
         <v>Aug</v>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="E19" s="3" t="n">
         <f aca="false">WEEKNUM(C19,21)</f>
         <v>32</v>
       </c>
-      <c r="K19" s="0" t="s">
+      <c r="K19" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L19" s="0" t="s">
+      <c r="L19" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C20" s="2" t="str">
-        <f aca="false">LEFT(K20,2)&amp;"/"&amp;MID(K20,4,2)&amp;"/"&amp;"20"&amp;MID(K20,7,2)&amp;MID(K20,FIND(" ",K20,1),6)</f>
-        <v>09/12/2021 06:00</v>
-      </c>
-      <c r="D20" s="2" t="str">
+      <c r="C20" s="3" t="str">
+        <f aca="false">LEFT(K20,2)&amp;"/"&amp;MID(K20,4,2)&amp;"/"&amp;MID(K20,7,2)&amp;MID(K20,FIND(" ",K20,1),6)</f>
+        <v>09/12/21 06:00</v>
+      </c>
+      <c r="D20" s="3" t="str">
         <f aca="false">TEXT(C20,"mmm")</f>
         <v>Sep</v>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" s="3" t="n">
         <f aca="false">WEEKNUM(C20,21)</f>
         <v>36</v>
       </c>
-      <c r="K20" s="0" t="s">
+      <c r="K20" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="L20" s="0" t="s">
+      <c r="L20" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C21" s="2" t="str">
-        <f aca="false">LEFT(K21,2)&amp;"/"&amp;MID(K21,4,2)&amp;"/"&amp;"20"&amp;MID(K21,7,2)&amp;MID(K21,FIND(" ",K21,1),6)</f>
-        <v>10/12/2021 13:54</v>
-      </c>
-      <c r="D21" s="2" t="str">
+      <c r="C21" s="3" t="str">
+        <f aca="false">LEFT(K21,2)&amp;"/"&amp;MID(K21,4,2)&amp;"/"&amp;MID(K21,7,2)&amp;MID(K21,FIND(" ",K21,1),6)</f>
+        <v>10/12/21 13:54</v>
+      </c>
+      <c r="D21" s="3" t="str">
         <f aca="false">TEXT(C21,"mmm")</f>
         <v>Oct</v>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E21" s="3" t="n">
         <f aca="false">WEEKNUM(C21,21)</f>
         <v>41</v>
       </c>
-      <c r="K21" s="0" t="s">
+      <c r="K21" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="L21" s="0" t="s">
+      <c r="L21" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C22" s="2" t="str">
-        <f aca="false">LEFT(K22,2)&amp;"/"&amp;MID(K22,4,2)&amp;"/"&amp;"20"&amp;MID(K22,7,2)&amp;MID(K22,FIND(" ",K22,1),6)</f>
-        <v>10/12/2021 18:00</v>
-      </c>
-      <c r="D22" s="2" t="str">
+      <c r="C22" s="3" t="str">
+        <f aca="false">LEFT(K22,2)&amp;"/"&amp;MID(K22,4,2)&amp;"/"&amp;MID(K22,7,2)&amp;MID(K22,FIND(" ",K22,1),6)</f>
+        <v>10/12/21 18:00</v>
+      </c>
+      <c r="D22" s="3" t="str">
         <f aca="false">TEXT(C22,"mmm")</f>
         <v>Oct</v>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E22" s="3" t="n">
         <f aca="false">WEEKNUM(C22,21)</f>
         <v>41</v>
       </c>
-      <c r="K22" s="0" t="s">
+      <c r="K22" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="L22" s="0" t="s">
+      <c r="L22" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C23" s="2" t="str">
-        <f aca="false">LEFT(K23,2)&amp;"/"&amp;MID(K23,4,2)&amp;"/"&amp;"20"&amp;MID(K23,7,2)&amp;MID(K23,FIND(" ",K23,1),6)</f>
-        <v>11/12/2021 18:00</v>
-      </c>
-      <c r="D23" s="2" t="str">
+      <c r="C23" s="3" t="str">
+        <f aca="false">LEFT(K23,2)&amp;"/"&amp;MID(K23,4,2)&amp;"/"&amp;MID(K23,7,2)&amp;MID(K23,FIND(" ",K23,1),6)</f>
+        <v>11/12/21 18:00</v>
+      </c>
+      <c r="D23" s="3" t="str">
         <f aca="false">TEXT(C23,"mmm")</f>
         <v>Nov</v>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E23" s="3" t="n">
         <f aca="false">WEEKNUM(C23,21)</f>
         <v>45</v>
       </c>
-      <c r="K23" s="0" t="s">
+      <c r="K23" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L23" s="0" t="s">
+      <c r="L23" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C24" s="2" t="str">
-        <f aca="false">LEFT(K24,2)&amp;"/"&amp;MID(K24,4,2)&amp;"/"&amp;"20"&amp;MID(K24,7,2)&amp;MID(K24,FIND(" ",K24,1),6)</f>
-        <v>14/12/2021 06:00</v>
-      </c>
-      <c r="D24" s="2" t="str">
+      <c r="C24" s="3" t="str">
+        <f aca="false">LEFT(K24,2)&amp;"/"&amp;MID(K24,4,2)&amp;"/"&amp;MID(K24,7,2)&amp;MID(K24,FIND(" ",K24,1),6)</f>
+        <v>14/12/21 06:00</v>
+      </c>
+      <c r="D24" s="3" t="str">
         <f aca="false">TEXT(C24,"mmm")</f>
-        <v>14/12/2021 06:00</v>
-      </c>
-      <c r="E24" s="2" t="e">
+        <v>14/12/21 06:00</v>
+      </c>
+      <c r="E24" s="3" t="e">
         <f aca="false">WEEKNUM(C24,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K24" s="0" t="s">
+      <c r="K24" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L24" s="0" t="s">
+      <c r="L24" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C25" s="2" t="str">
-        <f aca="false">LEFT(K25,2)&amp;"/"&amp;MID(K25,4,2)&amp;"/"&amp;"20"&amp;MID(K25,7,2)&amp;MID(K25,FIND(" ",K25,1),6)</f>
-        <v>15/12/2021 06:00</v>
-      </c>
-      <c r="D25" s="2" t="str">
+      <c r="C25" s="3" t="str">
+        <f aca="false">LEFT(K25,2)&amp;"/"&amp;MID(K25,4,2)&amp;"/"&amp;MID(K25,7,2)&amp;MID(K25,FIND(" ",K25,1),6)</f>
+        <v>15/12/21 06:00</v>
+      </c>
+      <c r="D25" s="3" t="str">
         <f aca="false">TEXT(C25,"mmm")</f>
-        <v>15/12/2021 06:00</v>
-      </c>
-      <c r="E25" s="2" t="e">
+        <v>15/12/21 06:00</v>
+      </c>
+      <c r="E25" s="3" t="e">
         <f aca="false">WEEKNUM(C25,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K25" s="0" t="s">
+      <c r="K25" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L25" s="0" t="s">
+      <c r="L25" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C26" s="2" t="str">
-        <f aca="false">LEFT(K26,2)&amp;"/"&amp;MID(K26,4,2)&amp;"/"&amp;"20"&amp;MID(K26,7,2)&amp;MID(K26,FIND(" ",K26,1),6)</f>
-        <v>16/12/2021 04:47</v>
-      </c>
-      <c r="D26" s="2" t="str">
+      <c r="C26" s="3" t="str">
+        <f aca="false">LEFT(K26,2)&amp;"/"&amp;MID(K26,4,2)&amp;"/"&amp;MID(K26,7,2)&amp;MID(K26,FIND(" ",K26,1),6)</f>
+        <v>16/12/21 04:47</v>
+      </c>
+      <c r="D26" s="3" t="str">
         <f aca="false">TEXT(C26,"mmm")</f>
-        <v>16/12/2021 04:47</v>
-      </c>
-      <c r="E26" s="2" t="e">
+        <v>16/12/21 04:47</v>
+      </c>
+      <c r="E26" s="3" t="e">
         <f aca="false">WEEKNUM(C26,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K26" s="0" t="s">
+      <c r="K26" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L26" s="0" t="s">
+      <c r="L26" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C27" s="2" t="str">
-        <f aca="false">LEFT(K27,2)&amp;"/"&amp;MID(K27,4,2)&amp;"/"&amp;"20"&amp;MID(K27,7,2)&amp;MID(K27,FIND(" ",K27,1),6)</f>
-        <v>16/12/2021 06:00</v>
-      </c>
-      <c r="D27" s="2" t="str">
+      <c r="C27" s="3" t="str">
+        <f aca="false">LEFT(K27,2)&amp;"/"&amp;MID(K27,4,2)&amp;"/"&amp;MID(K27,7,2)&amp;MID(K27,FIND(" ",K27,1),6)</f>
+        <v>16/12/21 06:00</v>
+      </c>
+      <c r="D27" s="3" t="str">
         <f aca="false">TEXT(C27,"mmm")</f>
-        <v>16/12/2021 06:00</v>
-      </c>
-      <c r="E27" s="2" t="e">
+        <v>16/12/21 06:00</v>
+      </c>
+      <c r="E27" s="3" t="e">
         <f aca="false">WEEKNUM(C27,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K27" s="0" t="s">
+      <c r="K27" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="L27" s="0" t="s">
+      <c r="L27" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C28" s="2" t="str">
-        <f aca="false">LEFT(K28,2)&amp;"/"&amp;MID(K28,4,2)&amp;"/"&amp;"20"&amp;MID(K28,7,2)&amp;MID(K28,FIND(" ",K28,1),6)</f>
-        <v>18/12/2021 18:00</v>
-      </c>
-      <c r="D28" s="2" t="str">
+      <c r="C28" s="3" t="str">
+        <f aca="false">LEFT(K28,2)&amp;"/"&amp;MID(K28,4,2)&amp;"/"&amp;MID(K28,7,2)&amp;MID(K28,FIND(" ",K28,1),6)</f>
+        <v>18/12/21 18:00</v>
+      </c>
+      <c r="D28" s="3" t="str">
         <f aca="false">TEXT(C28,"mmm")</f>
-        <v>18/12/2021 18:00</v>
-      </c>
-      <c r="E28" s="2" t="e">
+        <v>18/12/21 18:00</v>
+      </c>
+      <c r="E28" s="3" t="e">
         <f aca="false">WEEKNUM(C28,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K28" s="0" t="s">
+      <c r="K28" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="L28" s="0" t="s">
+      <c r="L28" s="1" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C29" s="2" t="str">
-        <f aca="false">LEFT(K29,2)&amp;"/"&amp;MID(K29,4,2)&amp;"/"&amp;"20"&amp;MID(K29,7,2)&amp;MID(K29,FIND(" ",K29,1),6)</f>
-        <v>19/12/2021 18:00</v>
-      </c>
-      <c r="D29" s="2" t="str">
+      <c r="C29" s="3" t="str">
+        <f aca="false">LEFT(K29,2)&amp;"/"&amp;MID(K29,4,2)&amp;"/"&amp;MID(K29,7,2)&amp;MID(K29,FIND(" ",K29,1),6)</f>
+        <v>19/12/21 18:00</v>
+      </c>
+      <c r="D29" s="3" t="str">
         <f aca="false">TEXT(C29,"mmm")</f>
-        <v>19/12/2021 18:00</v>
-      </c>
-      <c r="E29" s="2" t="e">
+        <v>19/12/21 18:00</v>
+      </c>
+      <c r="E29" s="3" t="e">
         <f aca="false">WEEKNUM(C29,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K29" s="0" t="s">
+      <c r="K29" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="L29" s="0" t="s">
+      <c r="L29" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C30" s="2" t="str">
-        <f aca="false">LEFT(K30,2)&amp;"/"&amp;MID(K30,4,2)&amp;"/"&amp;"20"&amp;MID(K30,7,2)&amp;MID(K30,FIND(" ",K30,1),6)</f>
-        <v>20/12/2021 07:07</v>
-      </c>
-      <c r="D30" s="2" t="str">
+      <c r="C30" s="3" t="str">
+        <f aca="false">LEFT(K30,2)&amp;"/"&amp;MID(K30,4,2)&amp;"/"&amp;MID(K30,7,2)&amp;MID(K30,FIND(" ",K30,1),6)</f>
+        <v>20/12/21 07:07</v>
+      </c>
+      <c r="D30" s="3" t="str">
         <f aca="false">TEXT(C30,"mmm")</f>
-        <v>20/12/2021 07:07</v>
-      </c>
-      <c r="E30" s="2" t="e">
+        <v>20/12/21 07:07</v>
+      </c>
+      <c r="E30" s="3" t="e">
         <f aca="false">WEEKNUM(C30,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K30" s="0" t="s">
+      <c r="K30" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="L30" s="0" t="s">
+      <c r="L30" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C31" s="2" t="str">
-        <f aca="false">LEFT(K31,2)&amp;"/"&amp;MID(K31,4,2)&amp;"/"&amp;"20"&amp;MID(K31,7,2)&amp;MID(K31,FIND(" ",K31,1),6)</f>
-        <v>20/12/2021 18:46</v>
-      </c>
-      <c r="D31" s="2" t="str">
+      <c r="C31" s="3" t="str">
+        <f aca="false">LEFT(K31,2)&amp;"/"&amp;MID(K31,4,2)&amp;"/"&amp;MID(K31,7,2)&amp;MID(K31,FIND(" ",K31,1),6)</f>
+        <v>20/12/21 18:46</v>
+      </c>
+      <c r="D31" s="3" t="str">
         <f aca="false">TEXT(C31,"mmm")</f>
-        <v>20/12/2021 18:46</v>
-      </c>
-      <c r="E31" s="2" t="e">
+        <v>20/12/21 18:46</v>
+      </c>
+      <c r="E31" s="3" t="e">
         <f aca="false">WEEKNUM(C31,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K31" s="0" t="s">
+      <c r="K31" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="L31" s="0" t="s">
+      <c r="L31" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C32" s="2" t="str">
-        <f aca="false">LEFT(K32,2)&amp;"/"&amp;MID(K32,4,2)&amp;"/"&amp;"20"&amp;MID(K32,7,2)&amp;MID(K32,FIND(" ",K32,1),6)</f>
-        <v>22/12/2021 06:00</v>
-      </c>
-      <c r="D32" s="2" t="str">
+      <c r="C32" s="3" t="str">
+        <f aca="false">LEFT(K32,2)&amp;"/"&amp;MID(K32,4,2)&amp;"/"&amp;MID(K32,7,2)&amp;MID(K32,FIND(" ",K32,1),6)</f>
+        <v>22/12/21 06:00</v>
+      </c>
+      <c r="D32" s="3" t="str">
         <f aca="false">TEXT(C32,"mmm")</f>
-        <v>22/12/2021 06:00</v>
-      </c>
-      <c r="E32" s="2" t="e">
+        <v>22/12/21 06:00</v>
+      </c>
+      <c r="E32" s="3" t="e">
         <f aca="false">WEEKNUM(C32,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K32" s="0" t="s">
+      <c r="K32" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="L32" s="0" t="s">
+      <c r="L32" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C33" s="2" t="str">
-        <f aca="false">LEFT(K33,2)&amp;"/"&amp;MID(K33,4,2)&amp;"/"&amp;"20"&amp;MID(K33,7,2)&amp;MID(K33,FIND(" ",K33,1),6)</f>
-        <v>23/12/2021 06:00</v>
-      </c>
-      <c r="D33" s="2" t="str">
+      <c r="C33" s="3" t="str">
+        <f aca="false">LEFT(K33,2)&amp;"/"&amp;MID(K33,4,2)&amp;"/"&amp;MID(K33,7,2)&amp;MID(K33,FIND(" ",K33,1),6)</f>
+        <v>23/12/21 06:00</v>
+      </c>
+      <c r="D33" s="3" t="str">
         <f aca="false">TEXT(C33,"mmm")</f>
-        <v>23/12/2021 06:00</v>
-      </c>
-      <c r="E33" s="2" t="e">
+        <v>23/12/21 06:00</v>
+      </c>
+      <c r="E33" s="3" t="e">
         <f aca="false">WEEKNUM(C33,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K33" s="0" t="s">
+      <c r="K33" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="L33" s="0" t="s">
+      <c r="L33" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C34" s="2" t="str">
-        <f aca="false">LEFT(K34,2)&amp;"/"&amp;MID(K34,4,2)&amp;"/"&amp;"20"&amp;MID(K34,7,2)&amp;MID(K34,FIND(" ",K34,1),6)</f>
-        <v>24/12/2021 06:00</v>
-      </c>
-      <c r="D34" s="2" t="str">
+      <c r="C34" s="3" t="str">
+        <f aca="false">LEFT(K34,2)&amp;"/"&amp;MID(K34,4,2)&amp;"/"&amp;MID(K34,7,2)&amp;MID(K34,FIND(" ",K34,1),6)</f>
+        <v>24/12/21 06:00</v>
+      </c>
+      <c r="D34" s="3" t="str">
         <f aca="false">TEXT(C34,"mmm")</f>
-        <v>24/12/2021 06:00</v>
-      </c>
-      <c r="E34" s="2" t="e">
+        <v>24/12/21 06:00</v>
+      </c>
+      <c r="E34" s="3" t="e">
         <f aca="false">WEEKNUM(C34,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K34" s="0" t="s">
+      <c r="K34" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="L34" s="0" t="s">
+      <c r="L34" s="1" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C35" s="2" t="str">
-        <f aca="false">LEFT(K35,2)&amp;"/"&amp;MID(K35,4,2)&amp;"/"&amp;"20"&amp;MID(K35,7,2)&amp;MID(K35,FIND(" ",K35,1),6)</f>
-        <v>01/01/2022 18:32</v>
-      </c>
-      <c r="D35" s="2" t="str">
+      <c r="C35" s="3" t="str">
+        <f aca="false">LEFT(K35,2)&amp;"/"&amp;MID(K35,4,2)&amp;"/"&amp;MID(K35,7,2)&amp;MID(K35,FIND(" ",K35,1),6)</f>
+        <v>01/01/22 18:32</v>
+      </c>
+      <c r="D35" s="3" t="str">
         <f aca="false">TEXT(C35,"mmm")</f>
         <v>Jan</v>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="E35" s="3" t="n">
         <f aca="false">WEEKNUM(C35,21)</f>
         <v>52</v>
       </c>
-      <c r="K35" s="0" t="s">
+      <c r="K35" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="L35" s="0" t="s">
+      <c r="L35" s="1" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C36" s="2" t="str">
-        <f aca="false">LEFT(K36,2)&amp;"/"&amp;MID(K36,4,2)&amp;"/"&amp;"20"&amp;MID(K36,7,2)&amp;MID(K36,FIND(" ",K36,1),6)</f>
-        <v>01/01/2022 21:52</v>
-      </c>
-      <c r="D36" s="2" t="str">
+      <c r="C36" s="3" t="str">
+        <f aca="false">LEFT(K36,2)&amp;"/"&amp;MID(K36,4,2)&amp;"/"&amp;MID(K36,7,2)&amp;MID(K36,FIND(" ",K36,1),6)</f>
+        <v>01/01/22 21:52</v>
+      </c>
+      <c r="D36" s="3" t="str">
         <f aca="false">TEXT(C36,"mmm")</f>
         <v>Jan</v>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="E36" s="3" t="n">
         <f aca="false">WEEKNUM(C36,21)</f>
         <v>52</v>
       </c>
-      <c r="K36" s="0" t="s">
+      <c r="K36" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="L36" s="0" t="s">
+      <c r="L36" s="1" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C37" s="2" t="str">
-        <f aca="false">LEFT(K37,2)&amp;"/"&amp;MID(K37,4,2)&amp;"/"&amp;"20"&amp;MID(K37,7,2)&amp;MID(K37,FIND(" ",K37,1),6)</f>
-        <v>03/01/2022 10:42</v>
-      </c>
-      <c r="D37" s="2" t="str">
+      <c r="C37" s="3" t="str">
+        <f aca="false">LEFT(K37,2)&amp;"/"&amp;MID(K37,4,2)&amp;"/"&amp;MID(K37,7,2)&amp;MID(K37,FIND(" ",K37,1),6)</f>
+        <v>03/01/22 10:42</v>
+      </c>
+      <c r="D37" s="3" t="str">
         <f aca="false">TEXT(C37,"mmm")</f>
         <v>Mar</v>
       </c>
-      <c r="E37" s="2" t="n">
+      <c r="E37" s="3" t="n">
         <f aca="false">WEEKNUM(C37,21)</f>
         <v>9</v>
       </c>
-      <c r="K37" s="0" t="s">
+      <c r="K37" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="L37" s="0" t="s">
+      <c r="L37" s="1" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C38" s="2" t="str">
-        <f aca="false">LEFT(K38,2)&amp;"/"&amp;MID(K38,4,2)&amp;"/"&amp;"20"&amp;MID(K38,7,2)&amp;MID(K38,FIND(" ",K38,1),6)</f>
-        <v>11/01/2022 17:25</v>
-      </c>
-      <c r="D38" s="2" t="str">
+      <c r="C38" s="3" t="str">
+        <f aca="false">LEFT(K38,2)&amp;"/"&amp;MID(K38,4,2)&amp;"/"&amp;MID(K38,7,2)&amp;MID(K38,FIND(" ",K38,1),6)</f>
+        <v>11/01/22 17:25</v>
+      </c>
+      <c r="D38" s="3" t="str">
         <f aca="false">TEXT(C38,"mmm")</f>
         <v>Nov</v>
       </c>
-      <c r="E38" s="2" t="n">
+      <c r="E38" s="3" t="n">
         <f aca="false">WEEKNUM(C38,21)</f>
         <v>44</v>
       </c>
-      <c r="K38" s="0" t="s">
+      <c r="K38" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="L38" s="0" t="s">
+      <c r="L38" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C39" s="2" t="str">
-        <f aca="false">LEFT(K39,2)&amp;"/"&amp;MID(K39,4,2)&amp;"/"&amp;"20"&amp;MID(K39,7,2)&amp;MID(K39,FIND(" ",K39,1),6)</f>
-        <v>13/01/2022 01:33</v>
-      </c>
-      <c r="D39" s="2" t="str">
+      <c r="C39" s="3" t="str">
+        <f aca="false">LEFT(K39,2)&amp;"/"&amp;MID(K39,4,2)&amp;"/"&amp;MID(K39,7,2)&amp;MID(K39,FIND(" ",K39,1),6)</f>
+        <v>13/01/22 01:33</v>
+      </c>
+      <c r="D39" s="3" t="str">
         <f aca="false">TEXT(C39,"mmm")</f>
-        <v>13/01/2022 01:33</v>
-      </c>
-      <c r="E39" s="2" t="e">
+        <v>13/01/22 01:33</v>
+      </c>
+      <c r="E39" s="3" t="e">
         <f aca="false">WEEKNUM(C39,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K39" s="0" t="s">
+      <c r="K39" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="L39" s="0" t="s">
+      <c r="L39" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C40" s="2" t="str">
-        <f aca="false">LEFT(K40,2)&amp;"/"&amp;MID(K40,4,2)&amp;"/"&amp;"20"&amp;MID(K40,7,2)&amp;MID(K40,FIND(" ",K40,1),6)</f>
-        <v>13/01/2022 17:11</v>
-      </c>
-      <c r="D40" s="2" t="str">
+      <c r="C40" s="3" t="str">
+        <f aca="false">LEFT(K40,2)&amp;"/"&amp;MID(K40,4,2)&amp;"/"&amp;MID(K40,7,2)&amp;MID(K40,FIND(" ",K40,1),6)</f>
+        <v>13/01/22 17:11</v>
+      </c>
+      <c r="D40" s="3" t="str">
         <f aca="false">TEXT(C40,"mmm")</f>
-        <v>13/01/2022 17:11</v>
-      </c>
-      <c r="E40" s="2" t="e">
+        <v>13/01/22 17:11</v>
+      </c>
+      <c r="E40" s="3" t="e">
         <f aca="false">WEEKNUM(C40,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K40" s="0" t="s">
+      <c r="K40" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="L40" s="0" t="s">
+      <c r="L40" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C41" s="2" t="str">
-        <f aca="false">LEFT(K41,2)&amp;"/"&amp;MID(K41,4,2)&amp;"/"&amp;"20"&amp;MID(K41,7,2)&amp;MID(K41,FIND(" ",K41,1),6)</f>
-        <v>14/01/2022 05:07</v>
-      </c>
-      <c r="D41" s="2" t="str">
+      <c r="C41" s="3" t="str">
+        <f aca="false">LEFT(K41,2)&amp;"/"&amp;MID(K41,4,2)&amp;"/"&amp;MID(K41,7,2)&amp;MID(K41,FIND(" ",K41,1),6)</f>
+        <v>14/01/22 05:07</v>
+      </c>
+      <c r="D41" s="3" t="str">
         <f aca="false">TEXT(C41,"mmm")</f>
-        <v>14/01/2022 05:07</v>
-      </c>
-      <c r="E41" s="2" t="e">
+        <v>14/01/22 05:07</v>
+      </c>
+      <c r="E41" s="3" t="e">
         <f aca="false">WEEKNUM(C41,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K41" s="0" t="s">
+      <c r="K41" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="L41" s="0" t="s">
+      <c r="L41" s="1" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C42" s="2" t="str">
-        <f aca="false">LEFT(K42,2)&amp;"/"&amp;MID(K42,4,2)&amp;"/"&amp;"20"&amp;MID(K42,7,2)&amp;MID(K42,FIND(" ",K42,1),6)</f>
-        <v>14/01/2022 20:45</v>
-      </c>
-      <c r="D42" s="2" t="str">
+      <c r="C42" s="3" t="str">
+        <f aca="false">LEFT(K42,2)&amp;"/"&amp;MID(K42,4,2)&amp;"/"&amp;MID(K42,7,2)&amp;MID(K42,FIND(" ",K42,1),6)</f>
+        <v>14/01/22 20:45</v>
+      </c>
+      <c r="D42" s="3" t="str">
         <f aca="false">TEXT(C42,"mmm")</f>
-        <v>14/01/2022 20:45</v>
-      </c>
-      <c r="E42" s="2" t="e">
+        <v>14/01/22 20:45</v>
+      </c>
+      <c r="E42" s="3" t="e">
         <f aca="false">WEEKNUM(C42,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K42" s="0" t="s">
+      <c r="K42" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="L42" s="0" t="s">
+      <c r="L42" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C43" s="2" t="str">
-        <f aca="false">LEFT(K43,2)&amp;"/"&amp;MID(K43,4,2)&amp;"/"&amp;"20"&amp;MID(K43,7,2)&amp;MID(K43,FIND(" ",K43,1),6)</f>
-        <v>14/01/2022 23:53</v>
-      </c>
-      <c r="D43" s="2" t="str">
+      <c r="C43" s="3" t="str">
+        <f aca="false">LEFT(K43,2)&amp;"/"&amp;MID(K43,4,2)&amp;"/"&amp;MID(K43,7,2)&amp;MID(K43,FIND(" ",K43,1),6)</f>
+        <v>14/01/22 23:53</v>
+      </c>
+      <c r="D43" s="3" t="str">
         <f aca="false">TEXT(C43,"mmm")</f>
-        <v>14/01/2022 23:53</v>
-      </c>
-      <c r="E43" s="2" t="e">
+        <v>14/01/22 23:53</v>
+      </c>
+      <c r="E43" s="3" t="e">
         <f aca="false">WEEKNUM(C43,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K43" s="0" t="s">
+      <c r="K43" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="L43" s="0" t="s">
+      <c r="L43" s="1" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C44" s="2" t="str">
-        <f aca="false">LEFT(K44,2)&amp;"/"&amp;MID(K44,4,2)&amp;"/"&amp;"20"&amp;MID(K44,7,2)&amp;MID(K44,FIND(" ",K44,1),6)</f>
-        <v>15/01/2022 06:08</v>
-      </c>
-      <c r="D44" s="2" t="str">
+      <c r="C44" s="3" t="str">
+        <f aca="false">LEFT(K44,2)&amp;"/"&amp;MID(K44,4,2)&amp;"/"&amp;MID(K44,7,2)&amp;MID(K44,FIND(" ",K44,1),6)</f>
+        <v>15/01/22 06:08</v>
+      </c>
+      <c r="D44" s="3" t="str">
         <f aca="false">TEXT(C44,"mmm")</f>
-        <v>15/01/2022 06:08</v>
-      </c>
-      <c r="E44" s="2" t="e">
+        <v>15/01/22 06:08</v>
+      </c>
+      <c r="E44" s="3" t="e">
         <f aca="false">WEEKNUM(C44,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K44" s="0" t="s">
+      <c r="K44" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="L44" s="0" t="s">
+      <c r="L44" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C45" s="2" t="str">
-        <f aca="false">LEFT(K45,2)&amp;"/"&amp;MID(K45,4,2)&amp;"/"&amp;"20"&amp;MID(K45,7,2)&amp;MID(K45,FIND(" ",K45,1),6)</f>
-        <v>15/01/2022 11:33</v>
-      </c>
-      <c r="D45" s="2" t="str">
+      <c r="C45" s="3" t="str">
+        <f aca="false">LEFT(K45,2)&amp;"/"&amp;MID(K45,4,2)&amp;"/"&amp;MID(K45,7,2)&amp;MID(K45,FIND(" ",K45,1),6)</f>
+        <v>15/01/22 11:33</v>
+      </c>
+      <c r="D45" s="3" t="str">
         <f aca="false">TEXT(C45,"mmm")</f>
-        <v>15/01/2022 11:33</v>
-      </c>
-      <c r="E45" s="2" t="e">
+        <v>15/01/22 11:33</v>
+      </c>
+      <c r="E45" s="3" t="e">
         <f aca="false">WEEKNUM(C45,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K45" s="0" t="s">
+      <c r="K45" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="L45" s="0" t="s">
+      <c r="L45" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C46" s="2" t="str">
-        <f aca="false">LEFT(K46,2)&amp;"/"&amp;MID(K46,4,2)&amp;"/"&amp;"20"&amp;MID(K46,7,2)&amp;MID(K46,FIND(" ",K46,1),6)</f>
-        <v>15/01/2022 18:13</v>
-      </c>
-      <c r="D46" s="2" t="str">
+      <c r="C46" s="3" t="str">
+        <f aca="false">LEFT(K46,2)&amp;"/"&amp;MID(K46,4,2)&amp;"/"&amp;MID(K46,7,2)&amp;MID(K46,FIND(" ",K46,1),6)</f>
+        <v>15/01/22 18:13</v>
+      </c>
+      <c r="D46" s="3" t="str">
         <f aca="false">TEXT(C46,"mmm")</f>
-        <v>15/01/2022 18:13</v>
-      </c>
-      <c r="E46" s="2" t="e">
+        <v>15/01/22 18:13</v>
+      </c>
+      <c r="E46" s="3" t="e">
         <f aca="false">WEEKNUM(C46,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K46" s="0" t="s">
+      <c r="K46" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="L46" s="0" t="s">
+      <c r="L46" s="1" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C47" s="2" t="str">
-        <f aca="false">LEFT(K47,2)&amp;"/"&amp;MID(K47,4,2)&amp;"/"&amp;"20"&amp;MID(K47,7,2)&amp;MID(K47,FIND(" ",K47,1),6)</f>
-        <v>16/01/2022 00:53</v>
-      </c>
-      <c r="D47" s="2" t="str">
+      <c r="C47" s="3" t="str">
+        <f aca="false">LEFT(K47,2)&amp;"/"&amp;MID(K47,4,2)&amp;"/"&amp;MID(K47,7,2)&amp;MID(K47,FIND(" ",K47,1),6)</f>
+        <v>16/01/22 00:53</v>
+      </c>
+      <c r="D47" s="3" t="str">
         <f aca="false">TEXT(C47,"mmm")</f>
-        <v>16/01/2022 00:53</v>
-      </c>
-      <c r="E47" s="2" t="e">
+        <v>16/01/22 00:53</v>
+      </c>
+      <c r="E47" s="3" t="e">
         <f aca="false">WEEKNUM(C47,21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K47" s="0" t="s">
+      <c r="K47" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L47" s="0" t="s">
+      <c r="L47" s="1" t="s">
         <v>71</v>
       </c>
     </row>

--- a/outputs/49196.xlsx
+++ b/outputs/49196.xlsx
@@ -640,12 +640,12 @@
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2" s="3" t="str">
-        <f aca="false">LEFT(K2,2)&amp;"/"&amp;MID(K2,4,2)&amp;"/"&amp;MID(K2,7,2)&amp;MID(K2,FIND(" ",K2,1),6)</f>
-        <v>21/11/21 14:28</v>
+        <f aca="false">LEFT(K2,2)&amp;"/"&amp;MID(K2,4,2)&amp;"/"&amp;"22"&amp;MID(K2,FIND(" ",K2,1),6)</f>
+        <v>21/11/22 14:28</v>
       </c>
       <c r="D2" s="3" t="str">
         <f aca="false">TEXT(C2,"mmm")</f>
-        <v>21/11/21 14:28</v>
+        <v>21/11/22 14:28</v>
       </c>
       <c r="E2" s="3" t="e">
         <f aca="false">WEEKNUM(C2,21)</f>
@@ -660,12 +660,12 @@
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="3" t="str">
-        <f aca="false">LEFT(K3,2)&amp;"/"&amp;MID(K3,4,2)&amp;"/"&amp;MID(K3,7,2)&amp;MID(K3,FIND(" ",K3,1),6)</f>
-        <v>22/11/21 06:00</v>
+        <f aca="false">LEFT(K3,2)&amp;"/"&amp;MID(K3,4,2)&amp;"/"&amp;"22"&amp;MID(K3,FIND(" ",K3,1),6)</f>
+        <v>22/11/22 06:00</v>
       </c>
       <c r="D3" s="3" t="str">
         <f aca="false">TEXT(C3,"mmm")</f>
-        <v>22/11/21 06:00</v>
+        <v>22/11/22 06:00</v>
       </c>
       <c r="E3" s="3" t="e">
         <f aca="false">WEEKNUM(C3,21)</f>
@@ -680,12 +680,12 @@
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="3" t="str">
-        <f aca="false">LEFT(K4,2)&amp;"/"&amp;MID(K4,4,2)&amp;"/"&amp;MID(K4,7,2)&amp;MID(K4,FIND(" ",K4,1),6)</f>
-        <v>23/11/21 06:00</v>
+        <f aca="false">LEFT(K4,2)&amp;"/"&amp;MID(K4,4,2)&amp;"/"&amp;"22"&amp;MID(K4,FIND(" ",K4,1),6)</f>
+        <v>23/11/22 06:00</v>
       </c>
       <c r="D4" s="3" t="str">
         <f aca="false">TEXT(C4,"mmm")</f>
-        <v>23/11/21 06:00</v>
+        <v>23/11/22 06:00</v>
       </c>
       <c r="E4" s="3" t="e">
         <f aca="false">WEEKNUM(C4,21)</f>
@@ -700,12 +700,12 @@
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C5" s="3" t="str">
-        <f aca="false">LEFT(K5,2)&amp;"/"&amp;MID(K5,4,2)&amp;"/"&amp;MID(K5,7,2)&amp;MID(K5,FIND(" ",K5,1),6)</f>
-        <v>23/11/21 22:04</v>
+        <f aca="false">LEFT(K5,2)&amp;"/"&amp;MID(K5,4,2)&amp;"/"&amp;"22"&amp;MID(K5,FIND(" ",K5,1),6)</f>
+        <v>23/11/22 22:04</v>
       </c>
       <c r="D5" s="3" t="str">
         <f aca="false">TEXT(C5,"mmm")</f>
-        <v>23/11/21 22:04</v>
+        <v>23/11/22 22:04</v>
       </c>
       <c r="E5" s="3" t="e">
         <f aca="false">WEEKNUM(C5,21)</f>
@@ -720,12 +720,12 @@
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C6" s="3" t="str">
-        <f aca="false">LEFT(K6,2)&amp;"/"&amp;MID(K6,4,2)&amp;"/"&amp;MID(K6,7,2)&amp;MID(K6,FIND(" ",K6,1),6)</f>
-        <v>24/11/21 18:00</v>
+        <f aca="false">LEFT(K6,2)&amp;"/"&amp;MID(K6,4,2)&amp;"/"&amp;"22"&amp;MID(K6,FIND(" ",K6,1),6)</f>
+        <v>24/11/22 18:00</v>
       </c>
       <c r="D6" s="3" t="str">
         <f aca="false">TEXT(C6,"mmm")</f>
-        <v>24/11/21 18:00</v>
+        <v>24/11/22 18:00</v>
       </c>
       <c r="E6" s="3" t="e">
         <f aca="false">WEEKNUM(C6,21)</f>
@@ -740,12 +740,12 @@
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="3" t="str">
-        <f aca="false">LEFT(K7,2)&amp;"/"&amp;MID(K7,4,2)&amp;"/"&amp;MID(K7,7,2)&amp;MID(K7,FIND(" ",K7,1),6)</f>
-        <v>25/11/21 18:00</v>
+        <f aca="false">LEFT(K7,2)&amp;"/"&amp;MID(K7,4,2)&amp;"/"&amp;"22"&amp;MID(K7,FIND(" ",K7,1),6)</f>
+        <v>25/11/22 18:00</v>
       </c>
       <c r="D7" s="3" t="str">
         <f aca="false">TEXT(C7,"mmm")</f>
-        <v>25/11/21 18:00</v>
+        <v>25/11/22 18:00</v>
       </c>
       <c r="E7" s="3" t="e">
         <f aca="false">WEEKNUM(C7,21)</f>
@@ -760,12 +760,12 @@
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C8" s="3" t="str">
-        <f aca="false">LEFT(K8,2)&amp;"/"&amp;MID(K8,4,2)&amp;"/"&amp;MID(K8,7,2)&amp;MID(K8,FIND(" ",K8,1),6)</f>
-        <v>26/11/21 10:13</v>
+        <f aca="false">LEFT(K8,2)&amp;"/"&amp;MID(K8,4,2)&amp;"/"&amp;"22"&amp;MID(K8,FIND(" ",K8,1),6)</f>
+        <v>26/11/22 10:13</v>
       </c>
       <c r="D8" s="3" t="str">
         <f aca="false">TEXT(C8,"mmm")</f>
-        <v>26/11/21 10:13</v>
+        <v>26/11/22 10:13</v>
       </c>
       <c r="E8" s="3" t="e">
         <f aca="false">WEEKNUM(C8,21)</f>
@@ -780,12 +780,12 @@
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C9" s="3" t="str">
-        <f aca="false">LEFT(K9,2)&amp;"/"&amp;MID(K9,4,2)&amp;"/"&amp;MID(K9,7,2)&amp;MID(K9,FIND(" ",K9,1),6)</f>
-        <v>29/11/21 19:18</v>
+        <f aca="false">LEFT(K9,2)&amp;"/"&amp;MID(K9,4,2)&amp;"/"&amp;"22"&amp;MID(K9,FIND(" ",K9,1),6)</f>
+        <v>29/11/22 19:18</v>
       </c>
       <c r="D9" s="3" t="str">
         <f aca="false">TEXT(C9,"mmm")</f>
-        <v>29/11/21 19:18</v>
+        <v>29/11/22 19:18</v>
       </c>
       <c r="E9" s="3" t="e">
         <f aca="false">WEEKNUM(C9,21)</f>
@@ -800,12 +800,12 @@
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="3" t="str">
-        <f aca="false">LEFT(K10,2)&amp;"/"&amp;MID(K10,4,2)&amp;"/"&amp;MID(K10,7,2)&amp;MID(K10,FIND(" ",K10,1),6)</f>
-        <v>30/11/21 05:04</v>
+        <f aca="false">LEFT(K10,2)&amp;"/"&amp;MID(K10,4,2)&amp;"/"&amp;"22"&amp;MID(K10,FIND(" ",K10,1),6)</f>
+        <v>30/11/22 05:04</v>
       </c>
       <c r="D10" s="3" t="str">
         <f aca="false">TEXT(C10,"mmm")</f>
-        <v>30/11/21 05:04</v>
+        <v>30/11/22 05:04</v>
       </c>
       <c r="E10" s="3" t="e">
         <f aca="false">WEEKNUM(C10,21)</f>
@@ -820,12 +820,12 @@
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C11" s="3" t="str">
-        <f aca="false">LEFT(K11,2)&amp;"/"&amp;MID(K11,4,2)&amp;"/"&amp;MID(K11,7,2)&amp;MID(K11,FIND(" ",K11,1),6)</f>
-        <v>30/11/21 06:00</v>
+        <f aca="false">LEFT(K11,2)&amp;"/"&amp;MID(K11,4,2)&amp;"/"&amp;"22"&amp;MID(K11,FIND(" ",K11,1),6)</f>
+        <v>30/11/22 06:00</v>
       </c>
       <c r="D11" s="3" t="str">
         <f aca="false">TEXT(C11,"mmm")</f>
-        <v>30/11/21 06:00</v>
+        <v>30/11/22 06:00</v>
       </c>
       <c r="E11" s="3" t="e">
         <f aca="false">WEEKNUM(C11,21)</f>
@@ -840,8 +840,8 @@
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C12" s="3" t="str">
-        <f aca="false">LEFT(K12,2)&amp;"/"&amp;MID(K12,4,2)&amp;"/"&amp;MID(K12,7,2)&amp;MID(K12,FIND(" ",K12,1),6)</f>
-        <v>01/12/21 00:02</v>
+        <f aca="false">LEFT(K12,2)&amp;"/"&amp;MID(K12,4,2)&amp;"/"&amp;"22"&amp;MID(K12,FIND(" ",K12,1),6)</f>
+        <v>01/12/22 00:02</v>
       </c>
       <c r="D12" s="3" t="str">
         <f aca="false">TEXT(C12,"mmm")</f>
@@ -860,8 +860,8 @@
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C13" s="3" t="str">
-        <f aca="false">LEFT(K13,2)&amp;"/"&amp;MID(K13,4,2)&amp;"/"&amp;MID(K13,7,2)&amp;MID(K13,FIND(" ",K13,1),6)</f>
-        <v>01/12/21 06:00</v>
+        <f aca="false">LEFT(K13,2)&amp;"/"&amp;MID(K13,4,2)&amp;"/"&amp;"22"&amp;MID(K13,FIND(" ",K13,1),6)</f>
+        <v>01/12/22 06:00</v>
       </c>
       <c r="D13" s="3" t="str">
         <f aca="false">TEXT(C13,"mmm")</f>
@@ -880,8 +880,8 @@
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C14" s="3" t="str">
-        <f aca="false">LEFT(K14,2)&amp;"/"&amp;MID(K14,4,2)&amp;"/"&amp;MID(K14,7,2)&amp;MID(K14,FIND(" ",K14,1),6)</f>
-        <v>02/12/21 01:43</v>
+        <f aca="false">LEFT(K14,2)&amp;"/"&amp;MID(K14,4,2)&amp;"/"&amp;"22"&amp;MID(K14,FIND(" ",K14,1),6)</f>
+        <v>02/12/22 01:43</v>
       </c>
       <c r="D14" s="3" t="str">
         <f aca="false">TEXT(C14,"mmm")</f>
@@ -900,8 +900,8 @@
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="3" t="str">
-        <f aca="false">LEFT(K15,2)&amp;"/"&amp;MID(K15,4,2)&amp;"/"&amp;MID(K15,7,2)&amp;MID(K15,FIND(" ",K15,1),6)</f>
-        <v>02/12/21 18:00</v>
+        <f aca="false">LEFT(K15,2)&amp;"/"&amp;MID(K15,4,2)&amp;"/"&amp;"22"&amp;MID(K15,FIND(" ",K15,1),6)</f>
+        <v>02/12/22 18:00</v>
       </c>
       <c r="D15" s="3" t="str">
         <f aca="false">TEXT(C15,"mmm")</f>
@@ -920,8 +920,8 @@
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C16" s="3" t="str">
-        <f aca="false">LEFT(K16,2)&amp;"/"&amp;MID(K16,4,2)&amp;"/"&amp;MID(K16,7,2)&amp;MID(K16,FIND(" ",K16,1),6)</f>
-        <v>03/12/21 18:00</v>
+        <f aca="false">LEFT(K16,2)&amp;"/"&amp;MID(K16,4,2)&amp;"/"&amp;"22"&amp;MID(K16,FIND(" ",K16,1),6)</f>
+        <v>03/12/22 18:00</v>
       </c>
       <c r="D16" s="3" t="str">
         <f aca="false">TEXT(C16,"mmm")</f>
@@ -940,8 +940,8 @@
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="3" t="str">
-        <f aca="false">LEFT(K17,2)&amp;"/"&amp;MID(K17,4,2)&amp;"/"&amp;MID(K17,7,2)&amp;MID(K17,FIND(" ",K17,1),6)</f>
-        <v>04/12/21 11:43</v>
+        <f aca="false">LEFT(K17,2)&amp;"/"&amp;MID(K17,4,2)&amp;"/"&amp;"22"&amp;MID(K17,FIND(" ",K17,1),6)</f>
+        <v>04/12/22 11:43</v>
       </c>
       <c r="D17" s="3" t="str">
         <f aca="false">TEXT(C17,"mmm")</f>
@@ -960,8 +960,8 @@
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="3" t="str">
-        <f aca="false">LEFT(K18,2)&amp;"/"&amp;MID(K18,4,2)&amp;"/"&amp;MID(K18,7,2)&amp;MID(K18,FIND(" ",K18,1),6)</f>
-        <v>08/12/21 00:54</v>
+        <f aca="false">LEFT(K18,2)&amp;"/"&amp;MID(K18,4,2)&amp;"/"&amp;"22"&amp;MID(K18,FIND(" ",K18,1),6)</f>
+        <v>08/12/22 00:54</v>
       </c>
       <c r="D18" s="3" t="str">
         <f aca="false">TEXT(C18,"mmm")</f>
@@ -980,8 +980,8 @@
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C19" s="3" t="str">
-        <f aca="false">LEFT(K19,2)&amp;"/"&amp;MID(K19,4,2)&amp;"/"&amp;MID(K19,7,2)&amp;MID(K19,FIND(" ",K19,1),6)</f>
-        <v>08/12/21 06:00</v>
+        <f aca="false">LEFT(K19,2)&amp;"/"&amp;MID(K19,4,2)&amp;"/"&amp;"22"&amp;MID(K19,FIND(" ",K19,1),6)</f>
+        <v>08/12/22 06:00</v>
       </c>
       <c r="D19" s="3" t="str">
         <f aca="false">TEXT(C19,"mmm")</f>
@@ -1000,8 +1000,8 @@
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C20" s="3" t="str">
-        <f aca="false">LEFT(K20,2)&amp;"/"&amp;MID(K20,4,2)&amp;"/"&amp;MID(K20,7,2)&amp;MID(K20,FIND(" ",K20,1),6)</f>
-        <v>09/12/21 06:00</v>
+        <f aca="false">LEFT(K20,2)&amp;"/"&amp;MID(K20,4,2)&amp;"/"&amp;"22"&amp;MID(K20,FIND(" ",K20,1),6)</f>
+        <v>09/12/22 06:00</v>
       </c>
       <c r="D20" s="3" t="str">
         <f aca="false">TEXT(C20,"mmm")</f>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="E20" s="3" t="n">
         <f aca="false">WEEKNUM(C20,21)</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>33</v>
@@ -1020,8 +1020,8 @@
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C21" s="3" t="str">
-        <f aca="false">LEFT(K21,2)&amp;"/"&amp;MID(K21,4,2)&amp;"/"&amp;MID(K21,7,2)&amp;MID(K21,FIND(" ",K21,1),6)</f>
-        <v>10/12/21 13:54</v>
+        <f aca="false">LEFT(K21,2)&amp;"/"&amp;MID(K21,4,2)&amp;"/"&amp;"22"&amp;MID(K21,FIND(" ",K21,1),6)</f>
+        <v>10/12/22 13:54</v>
       </c>
       <c r="D21" s="3" t="str">
         <f aca="false">TEXT(C21,"mmm")</f>
@@ -1040,8 +1040,8 @@
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C22" s="3" t="str">
-        <f aca="false">LEFT(K22,2)&amp;"/"&amp;MID(K22,4,2)&amp;"/"&amp;MID(K22,7,2)&amp;MID(K22,FIND(" ",K22,1),6)</f>
-        <v>10/12/21 18:00</v>
+        <f aca="false">LEFT(K22,2)&amp;"/"&amp;MID(K22,4,2)&amp;"/"&amp;"22"&amp;MID(K22,FIND(" ",K22,1),6)</f>
+        <v>10/12/22 18:00</v>
       </c>
       <c r="D22" s="3" t="str">
         <f aca="false">TEXT(C22,"mmm")</f>
@@ -1060,8 +1060,8 @@
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="3" t="str">
-        <f aca="false">LEFT(K23,2)&amp;"/"&amp;MID(K23,4,2)&amp;"/"&amp;MID(K23,7,2)&amp;MID(K23,FIND(" ",K23,1),6)</f>
-        <v>11/12/21 18:00</v>
+        <f aca="false">LEFT(K23,2)&amp;"/"&amp;MID(K23,4,2)&amp;"/"&amp;"22"&amp;MID(K23,FIND(" ",K23,1),6)</f>
+        <v>11/12/22 18:00</v>
       </c>
       <c r="D23" s="3" t="str">
         <f aca="false">TEXT(C23,"mmm")</f>
@@ -1080,12 +1080,12 @@
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="3" t="str">
-        <f aca="false">LEFT(K24,2)&amp;"/"&amp;MID(K24,4,2)&amp;"/"&amp;MID(K24,7,2)&amp;MID(K24,FIND(" ",K24,1),6)</f>
-        <v>14/12/21 06:00</v>
+        <f aca="false">LEFT(K24,2)&amp;"/"&amp;MID(K24,4,2)&amp;"/"&amp;"22"&amp;MID(K24,FIND(" ",K24,1),6)</f>
+        <v>14/12/22 06:00</v>
       </c>
       <c r="D24" s="3" t="str">
         <f aca="false">TEXT(C24,"mmm")</f>
-        <v>14/12/21 06:00</v>
+        <v>14/12/22 06:00</v>
       </c>
       <c r="E24" s="3" t="e">
         <f aca="false">WEEKNUM(C24,21)</f>
@@ -1100,12 +1100,12 @@
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="3" t="str">
-        <f aca="false">LEFT(K25,2)&amp;"/"&amp;MID(K25,4,2)&amp;"/"&amp;MID(K25,7,2)&amp;MID(K25,FIND(" ",K25,1),6)</f>
-        <v>15/12/21 06:00</v>
+        <f aca="false">LEFT(K25,2)&amp;"/"&amp;MID(K25,4,2)&amp;"/"&amp;"22"&amp;MID(K25,FIND(" ",K25,1),6)</f>
+        <v>15/12/22 06:00</v>
       </c>
       <c r="D25" s="3" t="str">
         <f aca="false">TEXT(C25,"mmm")</f>
-        <v>15/12/21 06:00</v>
+        <v>15/12/22 06:00</v>
       </c>
       <c r="E25" s="3" t="e">
         <f aca="false">WEEKNUM(C25,21)</f>
@@ -1120,12 +1120,12 @@
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="3" t="str">
-        <f aca="false">LEFT(K26,2)&amp;"/"&amp;MID(K26,4,2)&amp;"/"&amp;MID(K26,7,2)&amp;MID(K26,FIND(" ",K26,1),6)</f>
-        <v>16/12/21 04:47</v>
+        <f aca="false">LEFT(K26,2)&amp;"/"&amp;MID(K26,4,2)&amp;"/"&amp;"22"&amp;MID(K26,FIND(" ",K26,1),6)</f>
+        <v>16/12/22 04:47</v>
       </c>
       <c r="D26" s="3" t="str">
         <f aca="false">TEXT(C26,"mmm")</f>
-        <v>16/12/21 04:47</v>
+        <v>16/12/22 04:47</v>
       </c>
       <c r="E26" s="3" t="e">
         <f aca="false">WEEKNUM(C26,21)</f>
@@ -1140,12 +1140,12 @@
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="3" t="str">
-        <f aca="false">LEFT(K27,2)&amp;"/"&amp;MID(K27,4,2)&amp;"/"&amp;MID(K27,7,2)&amp;MID(K27,FIND(" ",K27,1),6)</f>
-        <v>16/12/21 06:00</v>
+        <f aca="false">LEFT(K27,2)&amp;"/"&amp;MID(K27,4,2)&amp;"/"&amp;"22"&amp;MID(K27,FIND(" ",K27,1),6)</f>
+        <v>16/12/22 06:00</v>
       </c>
       <c r="D27" s="3" t="str">
         <f aca="false">TEXT(C27,"mmm")</f>
-        <v>16/12/21 06:00</v>
+        <v>16/12/22 06:00</v>
       </c>
       <c r="E27" s="3" t="e">
         <f aca="false">WEEKNUM(C27,21)</f>
@@ -1160,12 +1160,12 @@
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="3" t="str">
-        <f aca="false">LEFT(K28,2)&amp;"/"&amp;MID(K28,4,2)&amp;"/"&amp;MID(K28,7,2)&amp;MID(K28,FIND(" ",K28,1),6)</f>
-        <v>18/12/21 18:00</v>
+        <f aca="false">LEFT(K28,2)&amp;"/"&amp;MID(K28,4,2)&amp;"/"&amp;"22"&amp;MID(K28,FIND(" ",K28,1),6)</f>
+        <v>18/12/22 18:00</v>
       </c>
       <c r="D28" s="3" t="str">
         <f aca="false">TEXT(C28,"mmm")</f>
-        <v>18/12/21 18:00</v>
+        <v>18/12/22 18:00</v>
       </c>
       <c r="E28" s="3" t="e">
         <f aca="false">WEEKNUM(C28,21)</f>
@@ -1180,12 +1180,12 @@
     </row>
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C29" s="3" t="str">
-        <f aca="false">LEFT(K29,2)&amp;"/"&amp;MID(K29,4,2)&amp;"/"&amp;MID(K29,7,2)&amp;MID(K29,FIND(" ",K29,1),6)</f>
-        <v>19/12/21 18:00</v>
+        <f aca="false">LEFT(K29,2)&amp;"/"&amp;MID(K29,4,2)&amp;"/"&amp;"22"&amp;MID(K29,FIND(" ",K29,1),6)</f>
+        <v>19/12/22 18:00</v>
       </c>
       <c r="D29" s="3" t="str">
         <f aca="false">TEXT(C29,"mmm")</f>
-        <v>19/12/21 18:00</v>
+        <v>19/12/22 18:00</v>
       </c>
       <c r="E29" s="3" t="e">
         <f aca="false">WEEKNUM(C29,21)</f>
@@ -1200,12 +1200,12 @@
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C30" s="3" t="str">
-        <f aca="false">LEFT(K30,2)&amp;"/"&amp;MID(K30,4,2)&amp;"/"&amp;MID(K30,7,2)&amp;MID(K30,FIND(" ",K30,1),6)</f>
-        <v>20/12/21 07:07</v>
+        <f aca="false">LEFT(K30,2)&amp;"/"&amp;MID(K30,4,2)&amp;"/"&amp;"22"&amp;MID(K30,FIND(" ",K30,1),6)</f>
+        <v>20/12/22 07:07</v>
       </c>
       <c r="D30" s="3" t="str">
         <f aca="false">TEXT(C30,"mmm")</f>
-        <v>20/12/21 07:07</v>
+        <v>20/12/22 07:07</v>
       </c>
       <c r="E30" s="3" t="e">
         <f aca="false">WEEKNUM(C30,21)</f>
@@ -1220,12 +1220,12 @@
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C31" s="3" t="str">
-        <f aca="false">LEFT(K31,2)&amp;"/"&amp;MID(K31,4,2)&amp;"/"&amp;MID(K31,7,2)&amp;MID(K31,FIND(" ",K31,1),6)</f>
-        <v>20/12/21 18:46</v>
+        <f aca="false">LEFT(K31,2)&amp;"/"&amp;MID(K31,4,2)&amp;"/"&amp;"22"&amp;MID(K31,FIND(" ",K31,1),6)</f>
+        <v>20/12/22 18:46</v>
       </c>
       <c r="D31" s="3" t="str">
         <f aca="false">TEXT(C31,"mmm")</f>
-        <v>20/12/21 18:46</v>
+        <v>20/12/22 18:46</v>
       </c>
       <c r="E31" s="3" t="e">
         <f aca="false">WEEKNUM(C31,21)</f>
@@ -1240,12 +1240,12 @@
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C32" s="3" t="str">
-        <f aca="false">LEFT(K32,2)&amp;"/"&amp;MID(K32,4,2)&amp;"/"&amp;MID(K32,7,2)&amp;MID(K32,FIND(" ",K32,1),6)</f>
-        <v>22/12/21 06:00</v>
+        <f aca="false">LEFT(K32,2)&amp;"/"&amp;MID(K32,4,2)&amp;"/"&amp;"22"&amp;MID(K32,FIND(" ",K32,1),6)</f>
+        <v>22/12/22 06:00</v>
       </c>
       <c r="D32" s="3" t="str">
         <f aca="false">TEXT(C32,"mmm")</f>
-        <v>22/12/21 06:00</v>
+        <v>22/12/22 06:00</v>
       </c>
       <c r="E32" s="3" t="e">
         <f aca="false">WEEKNUM(C32,21)</f>
@@ -1260,12 +1260,12 @@
     </row>
     <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C33" s="3" t="str">
-        <f aca="false">LEFT(K33,2)&amp;"/"&amp;MID(K33,4,2)&amp;"/"&amp;MID(K33,7,2)&amp;MID(K33,FIND(" ",K33,1),6)</f>
-        <v>23/12/21 06:00</v>
+        <f aca="false">LEFT(K33,2)&amp;"/"&amp;MID(K33,4,2)&amp;"/"&amp;"22"&amp;MID(K33,FIND(" ",K33,1),6)</f>
+        <v>23/12/22 06:00</v>
       </c>
       <c r="D33" s="3" t="str">
         <f aca="false">TEXT(C33,"mmm")</f>
-        <v>23/12/21 06:00</v>
+        <v>23/12/22 06:00</v>
       </c>
       <c r="E33" s="3" t="e">
         <f aca="false">WEEKNUM(C33,21)</f>
@@ -1280,12 +1280,12 @@
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C34" s="3" t="str">
-        <f aca="false">LEFT(K34,2)&amp;"/"&amp;MID(K34,4,2)&amp;"/"&amp;MID(K34,7,2)&amp;MID(K34,FIND(" ",K34,1),6)</f>
-        <v>24/12/21 06:00</v>
+        <f aca="false">LEFT(K34,2)&amp;"/"&amp;MID(K34,4,2)&amp;"/"&amp;"22"&amp;MID(K34,FIND(" ",K34,1),6)</f>
+        <v>24/12/22 06:00</v>
       </c>
       <c r="D34" s="3" t="str">
         <f aca="false">TEXT(C34,"mmm")</f>
-        <v>24/12/21 06:00</v>
+        <v>24/12/22 06:00</v>
       </c>
       <c r="E34" s="3" t="e">
         <f aca="false">WEEKNUM(C34,21)</f>
@@ -1300,7 +1300,7 @@
     </row>
     <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C35" s="3" t="str">
-        <f aca="false">LEFT(K35,2)&amp;"/"&amp;MID(K35,4,2)&amp;"/"&amp;MID(K35,7,2)&amp;MID(K35,FIND(" ",K35,1),6)</f>
+        <f aca="false">LEFT(K35,2)&amp;"/"&amp;MID(K35,4,2)&amp;"/"&amp;"22"&amp;MID(K35,FIND(" ",K35,1),6)</f>
         <v>01/01/22 18:32</v>
       </c>
       <c r="D35" s="3" t="str">
@@ -1320,7 +1320,7 @@
     </row>
     <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C36" s="3" t="str">
-        <f aca="false">LEFT(K36,2)&amp;"/"&amp;MID(K36,4,2)&amp;"/"&amp;MID(K36,7,2)&amp;MID(K36,FIND(" ",K36,1),6)</f>
+        <f aca="false">LEFT(K36,2)&amp;"/"&amp;MID(K36,4,2)&amp;"/"&amp;"22"&amp;MID(K36,FIND(" ",K36,1),6)</f>
         <v>01/01/22 21:52</v>
       </c>
       <c r="D36" s="3" t="str">
@@ -1340,7 +1340,7 @@
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C37" s="3" t="str">
-        <f aca="false">LEFT(K37,2)&amp;"/"&amp;MID(K37,4,2)&amp;"/"&amp;MID(K37,7,2)&amp;MID(K37,FIND(" ",K37,1),6)</f>
+        <f aca="false">LEFT(K37,2)&amp;"/"&amp;MID(K37,4,2)&amp;"/"&amp;"22"&amp;MID(K37,FIND(" ",K37,1),6)</f>
         <v>03/01/22 10:42</v>
       </c>
       <c r="D37" s="3" t="str">
@@ -1360,7 +1360,7 @@
     </row>
     <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C38" s="3" t="str">
-        <f aca="false">LEFT(K38,2)&amp;"/"&amp;MID(K38,4,2)&amp;"/"&amp;MID(K38,7,2)&amp;MID(K38,FIND(" ",K38,1),6)</f>
+        <f aca="false">LEFT(K38,2)&amp;"/"&amp;MID(K38,4,2)&amp;"/"&amp;"22"&amp;MID(K38,FIND(" ",K38,1),6)</f>
         <v>11/01/22 17:25</v>
       </c>
       <c r="D38" s="3" t="str">
@@ -1380,7 +1380,7 @@
     </row>
     <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C39" s="3" t="str">
-        <f aca="false">LEFT(K39,2)&amp;"/"&amp;MID(K39,4,2)&amp;"/"&amp;MID(K39,7,2)&amp;MID(K39,FIND(" ",K39,1),6)</f>
+        <f aca="false">LEFT(K39,2)&amp;"/"&amp;MID(K39,4,2)&amp;"/"&amp;"22"&amp;MID(K39,FIND(" ",K39,1),6)</f>
         <v>13/01/22 01:33</v>
       </c>
       <c r="D39" s="3" t="str">
@@ -1400,7 +1400,7 @@
     </row>
     <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C40" s="3" t="str">
-        <f aca="false">LEFT(K40,2)&amp;"/"&amp;MID(K40,4,2)&amp;"/"&amp;MID(K40,7,2)&amp;MID(K40,FIND(" ",K40,1),6)</f>
+        <f aca="false">LEFT(K40,2)&amp;"/"&amp;MID(K40,4,2)&amp;"/"&amp;"22"&amp;MID(K40,FIND(" ",K40,1),6)</f>
         <v>13/01/22 17:11</v>
       </c>
       <c r="D40" s="3" t="str">
@@ -1420,7 +1420,7 @@
     </row>
     <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C41" s="3" t="str">
-        <f aca="false">LEFT(K41,2)&amp;"/"&amp;MID(K41,4,2)&amp;"/"&amp;MID(K41,7,2)&amp;MID(K41,FIND(" ",K41,1),6)</f>
+        <f aca="false">LEFT(K41,2)&amp;"/"&amp;MID(K41,4,2)&amp;"/"&amp;"22"&amp;MID(K41,FIND(" ",K41,1),6)</f>
         <v>14/01/22 05:07</v>
       </c>
       <c r="D41" s="3" t="str">
@@ -1440,7 +1440,7 @@
     </row>
     <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C42" s="3" t="str">
-        <f aca="false">LEFT(K42,2)&amp;"/"&amp;MID(K42,4,2)&amp;"/"&amp;MID(K42,7,2)&amp;MID(K42,FIND(" ",K42,1),6)</f>
+        <f aca="false">LEFT(K42,2)&amp;"/"&amp;MID(K42,4,2)&amp;"/"&amp;"22"&amp;MID(K42,FIND(" ",K42,1),6)</f>
         <v>14/01/22 20:45</v>
       </c>
       <c r="D42" s="3" t="str">
@@ -1460,7 +1460,7 @@
     </row>
     <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C43" s="3" t="str">
-        <f aca="false">LEFT(K43,2)&amp;"/"&amp;MID(K43,4,2)&amp;"/"&amp;MID(K43,7,2)&amp;MID(K43,FIND(" ",K43,1),6)</f>
+        <f aca="false">LEFT(K43,2)&amp;"/"&amp;MID(K43,4,2)&amp;"/"&amp;"22"&amp;MID(K43,FIND(" ",K43,1),6)</f>
         <v>14/01/22 23:53</v>
       </c>
       <c r="D43" s="3" t="str">
@@ -1480,7 +1480,7 @@
     </row>
     <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C44" s="3" t="str">
-        <f aca="false">LEFT(K44,2)&amp;"/"&amp;MID(K44,4,2)&amp;"/"&amp;MID(K44,7,2)&amp;MID(K44,FIND(" ",K44,1),6)</f>
+        <f aca="false">LEFT(K44,2)&amp;"/"&amp;MID(K44,4,2)&amp;"/"&amp;"22"&amp;MID(K44,FIND(" ",K44,1),6)</f>
         <v>15/01/22 06:08</v>
       </c>
       <c r="D44" s="3" t="str">
@@ -1500,7 +1500,7 @@
     </row>
     <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C45" s="3" t="str">
-        <f aca="false">LEFT(K45,2)&amp;"/"&amp;MID(K45,4,2)&amp;"/"&amp;MID(K45,7,2)&amp;MID(K45,FIND(" ",K45,1),6)</f>
+        <f aca="false">LEFT(K45,2)&amp;"/"&amp;MID(K45,4,2)&amp;"/"&amp;"22"&amp;MID(K45,FIND(" ",K45,1),6)</f>
         <v>15/01/22 11:33</v>
       </c>
       <c r="D45" s="3" t="str">
@@ -1520,7 +1520,7 @@
     </row>
     <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C46" s="3" t="str">
-        <f aca="false">LEFT(K46,2)&amp;"/"&amp;MID(K46,4,2)&amp;"/"&amp;MID(K46,7,2)&amp;MID(K46,FIND(" ",K46,1),6)</f>
+        <f aca="false">LEFT(K46,2)&amp;"/"&amp;MID(K46,4,2)&amp;"/"&amp;"22"&amp;MID(K46,FIND(" ",K46,1),6)</f>
         <v>15/01/22 18:13</v>
       </c>
       <c r="D46" s="3" t="str">
@@ -1540,7 +1540,7 @@
     </row>
     <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C47" s="3" t="str">
-        <f aca="false">LEFT(K47,2)&amp;"/"&amp;MID(K47,4,2)&amp;"/"&amp;MID(K47,7,2)&amp;MID(K47,FIND(" ",K47,1),6)</f>
+        <f aca="false">LEFT(K47,2)&amp;"/"&amp;MID(K47,4,2)&amp;"/"&amp;"22"&amp;MID(K47,FIND(" ",K47,1),6)</f>
         <v>16/01/22 00:53</v>
       </c>
       <c r="D47" s="3" t="str">
